--- a/COVER Corporation_next_7_days.xlsx
+++ b/COVER Corporation_next_7_days.xlsx
@@ -443,71 +443,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1541</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1557</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1551</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1539</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1539</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1526</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1532</v>
+        <v>1581</v>
       </c>
     </row>
   </sheetData>
